--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G465"/>
+  <dimension ref="A1:G470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10197,6 +10197,111 @@
         </is>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Synthetic Dementia Dataset (India, LASI-Anchored)</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/drsuvish/synthetic-dementia-dataset-lmic</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>A Multi-Clinic Dental Panoramic Radiograph Dataset</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nafeesalmahadi/a-multi-clinic-dental-panoramic-radiograph-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Merged Glaucoma Fundus Dataset (ORIGA + ACRIMA)</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Fundus</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/abdullah65621/glaucoma-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Data-Set de paciente con Fibromatosis Gingival Idiopática (FGI)</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>CBCT</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/NFDJQ6</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>3D Cell Culture Confocal Images for Glioblastoma &amp; Astrocyte Interaction</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Confocal Microscopy</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr"/>
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/QRYIQZ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G470"/>
+  <dimension ref="A1:G477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10302,6 +10302,153 @@
         </is>
       </c>
     </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Smart MRI Detection</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/riachk/smart-mri-detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>thanminh01/NSCLC-THESIS-WSI-DATASET-EMBEDDING</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/thanminh01/NSCLC-THESIS-WSI-DATASET-EMBEDDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Forearm Ultrasound Dataset for Hand Gesture Classification and Finger Joint Angle Estimation</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21825018</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Large-Scale Functional Brain Network Organization Is Largely Preserved in Neuropathic Pain Despite Selective Circuit-Level Adaptations - 2d dataset</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr"/>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21836173</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Large-Scale Functional Brain Network Organization Is Largely Preserved in Neuropathic Pain Despite Selective Circuit-Level Adaptations - Dataset-1</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr"/>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21838853</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Annotated Whole-Slide Images of Core Needle Prostate Biopsies</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
+      <c r="C476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr"/>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21780258</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Output Dataset: Processed Adversarial Sensitivity Maps and Trained Models Derived from TCGA-BRCA for Triple Negative Breast Cancer Analysis</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr"/>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/VWT2W8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G477"/>
+  <dimension ref="A1:G482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10449,6 +10449,111 @@
         </is>
       </c>
     </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>BreastDCEDL: 3D Breast MRI Dataset</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/programminghero009/breast-dcedl</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Chest CT Images and Segmentation Masks Dataset</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/rahult25/chest-ct-images-and-segmentation-masks-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Dental Radiography - Cropped Multi Class Dataset</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/retrospwn/dental-radiography-cropped-multi-class-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>SEMICON v2 Dual Dataset</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr"/>
+      <c r="C481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/omkadam05/semicon-v2-dual-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Wide Angle X-Ray Scattering Data Set of Gypsum Compounds</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr"/>
+      <c r="C482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21849209</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G482"/>
+  <dimension ref="A1:G484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10554,6 +10554,48 @@
         </is>
       </c>
     </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Explainable Brain Tumor Detection Using EfficientNetV2-S and RBF-SVM: A Multi-Source MRI Study — Reproducibility Archive</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr"/>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21855712</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>TAT-Det: A Dataset for Testicular Appendage Torsion Detection and Segmentation in Ultrasound Images</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr"/>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21861476</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G484"/>
+  <dimension ref="A1:G490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10596,6 +10596,132 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Augmented Dataset (MRI)</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/teammindnova/augmented-dataset-mri</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Dataset for "High-resolution nanoimaging reference study of a cement paste by near-field ptychographic X-ray computed tomography" paper</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/14176601</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Dataset and Scripts for "Application of SAP-X2C to Spectroscopy and Comparison to Screened Nuclear Spin-Orbit Approximations"</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr"/>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21879659</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Trained model weights for "Lightweight attention mechanisms in breast ultrasound lesion segmentation: parameter cost, protocol choice, data leakage, and what the data can resolve"</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr"/>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21870651</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Comprehensive Patient Level Dataset for a Systematic Review of Melorheostosis Clinical Presentation, Imaging Features, and Treatment Outcomes</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr"/>
+      <c r="C489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21881461</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Supplementary Materials for the article "2D Adaptive Multi-Interval Scale (AMIS): Method for Per-Cell Normalization and Visualization of Spatial Heterogeneous Data"</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr"/>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Echocardiography</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/BXFEVO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G490"/>
+  <dimension ref="A1:G501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10722,6 +10722,237 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>main dataset 1</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr"/>
+      <c r="C491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/happysruti/main-dataset-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Brain MRI and Chest X-ray Dataset</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr"/>
+      <c r="C492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ap25122040025/brain-mri-and-chest-x-ray-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Results analysis results of thigh MRI segmentation by various algorithms</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr"/>
+      <c r="C493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21840980</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Do Quantum Kernels Degrade Less Under Chest X-ray Preprocessing Shift? A Leakage-Controlled Cross-Pipeline Benchmark</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr"/>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21892565</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Benchmark dataset for quantitative validation of Carbon K-edge soft X-ray spectroptychography</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr"/>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21890394</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Dataset for "Ultrafast laser-induced surface modification of Kanthal® AF: Morphology, chemistry, and wettability under ambient conditions"</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr"/>
+      <c r="C496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr"/>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21887932</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>MgKdb: A dataset of curated magnesium and potassium ions annotated on cyo-em structure</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr"/>
+      <c r="C497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr"/>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21886714</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Dataset of "In situ activation mechanisms governing the stabilization through the optimal core-shell formation in bimetallic Ir-Ru catalysts"</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr"/>
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21884683</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Validation Dataset for "Entomoscope 2.0 and ENIMAS 2.0: An Open-Source, AI-Integrated Platform for Rapid and Affordable Insect Digitization"</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr"/>
+      <c r="C499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21892852</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>A georeferenced dataset for grapevine phenology and phytosanitary monitoring across Italy</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr"/>
+      <c r="C500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21534581</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Clonal Seborrheic Keratoses and Control Images for Annotation</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr"/>
+      <c r="C501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>https://api.isic-archive.com/collections/476</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G501"/>
+  <dimension ref="A1:G511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10953,6 +10953,216 @@
         </is>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>mriadur/phishing-email-dataset</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/mriadur/phishing-email-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Dataset for "De-aberration for noninvasive transcranial photoacoustic computed tomography through an adult human skull"</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21896253</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>microCT dataset of Oerstedia sp. (SIO-BIC W10325) - HOLOTYPE</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr"/>
+      <c r="C504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Micro-CT</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr"/>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21901180</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>microCT dataset of Amphiporus sanakensis n.sp. (SIO-BIC W10103) - HOLOTYPE</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr"/>
+      <c r="C505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Micro-CT</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr"/>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21900726</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>microCT dataset of Sagornya tatjanae (SIO-BIC W10090)</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr"/>
+      <c r="C506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Micro-CT</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21902363</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Hazelnut X-ray classification benchmark: images, labels and reference results</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr"/>
+      <c r="C507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21739932</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Dataset for: Midair Single-Sided Acoustic Levitation in High-Pressure Regions of Zero-Order Bessel Beams</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr"/>
+      <c r="C508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr"/>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21464854</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Sperm chromatin dispersion microscopy image dataset for instance segmentation</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr"/>
+      <c r="C509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr"/>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21628868</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Adaptive Polishing: SEM training data &amp; machine-learning segmentation models</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr"/>
+      <c r="C510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr"/>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21804785</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Noise-aware dynamic convolution for improved generalizability of retinal disease diagnosis using optical coherence tomography images.</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr"/>
+      <c r="C511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr"/>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13464582/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G511"/>
+  <dimension ref="A1:G515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11163,6 +11163,90 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>VetXRay: Comprehensive Animal Chest X-Ray Dataset</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr"/>
+      <c r="C512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr"/>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/mahyarmj/vetxray-animal-dataset-complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>SSR Reasoning: PlantVillage Improved Dataset</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr"/>
+      <c r="C513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr"/>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/amith1707/plantvillage-improved-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Citrus Leaf Pathology Multi-Class Image Dataset</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr"/>
+      <c r="C514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Pathology</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr"/>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/chayanmondalabir/citrus-leaf-pathology-multi-class-image-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Mrisaac/my-test-dataset</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr"/>
+      <c r="C515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr"/>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/Mrisaac/my-test-dataset</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G515"/>
+  <dimension ref="A1:G523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11247,6 +11247,174 @@
         </is>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>brain-tumor-mri-dataset-V1</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr"/>
+      <c r="C516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr"/>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ashikkhan02/brain-tumor-mri-dataset-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>brain tumor dataset</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr"/>
+      <c r="C517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/adityagangji/brain-tumor-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>IQ-OTH/NCCD Lung Cancer CT Scan Dataset</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr"/>
+      <c r="C518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/programminghero009/lung-cancer</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>BoneLoss-PAN769: Expert-Annotated Panoramic Radiograph Dataset for Periodontal Bone-Loss Assessment</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr"/>
+      <c r="C519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21939261</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Dataset for study 'Multi-season evaluation of temperature and wind in the marine boundary layer along the United States northeast coast in the High-Resolution Rapid Refresh model'</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr"/>
+      <c r="C520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21938359</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Dataset for journal article "Soft Matter Self-Assembly: From Droplets to Myelin Figures"</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
+      <c r="C521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21619314</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>A Systematically Designed Open-Access SEM Dataset and Robustness Benchmark for Machine Learning-Based Microstructure Segmentation: A High-Chromium Cast Iron Case Study</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr"/>
+      <c r="C522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21931379</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>MicrobeNetNet Dataset Review Corpus and Associated Data Products hash://md5/5981a37a16c25204dc18d9188f185b19 hash://sha256/7448991edd5f79db02519a5b3d4691c50a60c02f45d40f087402a7a492da3a3e</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr"/>
+      <c r="C523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21940611</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G523"/>
+  <dimension ref="A1:G525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11415,6 +11415,48 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Women's Health - PubMed Dataset 1786 - 2026</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr"/>
+      <c r="C524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr"/>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/shanti33/womens-health-pubmed-dataset-1786-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Women's Health - Clinical Trials Dataset 1968-2026</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr"/>
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr"/>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/shanti33/womens-health-clinical-trials-dataset-1968-2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G525"/>
+  <dimension ref="A1:G526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11457,6 +11457,27 @@
         </is>
       </c>
     </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>BUSI dataset</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr"/>
+      <c r="C526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/arpanc6/busi-dataset</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G526"/>
+  <dimension ref="A1:G529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11478,6 +11478,69 @@
         </is>
       </c>
     </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Chest X-ray dataset for lung segmentation</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr"/>
+      <c r="C527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr"/>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/projectmantra/chest-x-ray-dataset-for-lung-segmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>NASA Turbofan Jet Engine Dataset CSV</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr"/>
+      <c r="C528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/azmaininqiadadeeb/nasa-turbofan-jet-engine-dataset-csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>OptoNet Dataset</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr"/>
+      <c r="C529" t="inlineStr"/>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr"/>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/mevltcangndoan/optonet-dataset</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G529"/>
+  <dimension ref="A1:G534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11541,6 +11541,111 @@
         </is>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Ortho-X Fracture X-Ray Dataset</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr"/>
+      <c r="C530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr"/>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/abdelrahman202626/ortho-x-fracture-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Algerian Ultrasound Images Thyroid Dataset</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr"/>
+      <c r="C531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr"/>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/rahatulislamshahi/algerian-ultrasound-images-thyroid-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>MultiEYE dataset</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr"/>
+      <c r="C532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/sophiestrzeliska/multieye</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>CTI_Pulseq Tutorial Dataset: Raw Phantom Diffusion MRI Data for Correlation Tensor Imaging (CTI)</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr"/>
+      <c r="C533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>dMRI</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr"/>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21991552</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>GlioTrace example dataset</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr"/>
+      <c r="C534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr"/>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21981544</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G534"/>
+  <dimension ref="A1:G558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11646,6 +11646,510 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>HAM10000 Skin Lesion Classification</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr"/>
+      <c r="C535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr"/>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/azimkhan031/ham10000-skin-lesion-classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Melanoma Skin Cancer Dataset - Benign vs Malignant</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr"/>
+      <c r="C536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ailearner-researchlab/melanoma-skin-cancer-dataset-benign-vs-malignant</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>ISIC 2018 Skin Lesion Segmentation Dataset</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr"/>
+      <c r="C537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr"/>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/idrissasi/isic2018-segmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Monkeypox dataset</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr"/>
+      <c r="C538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ramanarasimhakanduri/monkeypox-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>PAD-UFES-20: a skin lesion dataset</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr"/>
+      <c r="C539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/rejaul5/pad-ufes-20-a-skin-lesion-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Skin Disease Detection Dataset (HAM10000 + ISIC)</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr"/>
+      <c r="C540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/theibrarbashir/skin-disease-detection-dataset-ham10000-isic</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>ISIC 2019 Skin Lesion Classification Dataset</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr"/>
+      <c r="C541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr"/>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ucimachinelearning/isic-2019-skin-lesion-classification-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>ISIC 2019 Sorted Disease Classification Dataset</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr"/>
+      <c r="C542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/tajmim/isic-2019-sorted-diease</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Bite and Skin Lesion Images Dataset</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr"/>
+      <c r="C543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/hibatallahdjokhdem/bite-and-skin-lesion-images-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Multi-Class Viral Skin Lesion Dataset (MCVSLD)</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr"/>
+      <c r="C544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr"/>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/borhan2003/multi-class-viral-skin-lesion-dataset-mcvsld</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Skin Lesion: HAM10000 (Image^Mask)</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+      <c r="C545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Dermoscopy</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/probaldeepto/skin-lesion-ham10000-imagemask</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>ISIC2019 Skin Cancer Dataset</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr"/>
+      <c r="C546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr"/>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/aeleyan/isic2019-skin-cancer-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Research-Grade Skin Disease Dataset</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr"/>
+      <c r="C547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr"/>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/happyparsi/research-grade-skin-disease-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Long-read RNA-seq dataset of X-ray–irradiated human whole blood</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr"/>
+      <c r="C548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr"/>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22013472</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Particle-resolved DNS dataset for orientation-dependent drag, lift, and torque correlations of Platonic polyhedral particles — Part 2: octahedron, dodecahedron, and icosahedron</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr"/>
+      <c r="C549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr"/>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22007965</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Gray et al - High frame rate in vivo two-photon microscopy (Data set 7)</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr"/>
+      <c r="C550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr"/>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22003335</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Gray et al - High frame rate in vivo two-photon microscopy (Data set 6)</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr"/>
+      <c r="C551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr"/>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22001106</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Gray et al - High frame rate in vivo two-photon microscopy (Data set 5)</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr"/>
+      <c r="C552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr"/>
+      <c r="F552" t="inlineStr"/>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21999588</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Gray et al - High frame rate in vivo two-photon microscopy (Data set 4)</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr"/>
+      <c r="C553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr"/>
+      <c r="F553" t="inlineStr"/>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21996239</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Gray et al - High frame rate in vivo two-photon microscopy (Data set 3)</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr"/>
+      <c r="C554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr"/>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21987053</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Gray et al - High frame rate in vivo two-photon microscopy (Data set 2)</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr"/>
+      <c r="C555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr"/>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21986688</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Gray et al - High frame rate in vivo two-photon microscopy (Data set 1)</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr"/>
+      <c r="C556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr"/>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21984497</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Derived Data and Analysis Code for Calibration-Aware Patient-Level Prediction of Microsatellite Instability in Colorectal Cancer from Whole-Slide Histopathology Images Using Foundation-Model Embeddings</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr"/>
+      <c r="C557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr"/>
+      <c r="F557" t="inlineStr"/>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22021667</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>[A semi-supervised MRI image segmentation dual-network model for regions with ambiguous boundaries and heterogeneous regions].</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr"/>
+      <c r="C558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr"/>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13458753/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G558"/>
+  <dimension ref="A1:G567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12150,6 +12150,195 @@
         </is>
       </c>
     </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Thyroid Cancer Ultrasound Dataset</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr"/>
+      <c r="C559" t="inlineStr"/>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr"/>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/abulkalamazad9867/thyroid-cancer-ultrasound-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Dataset-OCTDL</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr"/>
+      <c r="C560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr"/>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/deepakraje24phd0186/dataset-octdl</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Molecular Docking Dataset for Native Ligand Validation (38Z/SCH772984) and Comparative Analysis of ASN007, Tizaterkib, Temuterkib, Rineterkib, and Ravoxertinib against Wild-Type Human MAPK3/ERK1 (PDB ID: 4QTB)</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr"/>
+      <c r="C561" t="inlineStr"/>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr"/>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22031357</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Dataset for Spatially Separated Dual Floating-Gate Synaptic Memory Based on Multilayer SnS2 for Neuromorphic Computing</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr"/>
+      <c r="C562" t="inlineStr"/>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr"/>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22025793</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Recurrent hospitalization in alcohol-related cirrhosis: de-identified patient-level and episode-level data with blinded chart-review classification, and analysis code</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr"/>
+      <c r="C563" t="inlineStr"/>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr"/>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22035277</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Microscopy image segmentation datasets with mask annotations</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr"/>
+      <c r="C564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr"/>
+      <c r="F564" t="inlineStr"/>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22039777</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Dataset for phSFC framework: Spectral Flow Cytometry and Hyperspectral Confocal Microscopy Files</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr"/>
+      <c r="C565" t="inlineStr"/>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Confocal Microscopy</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr"/>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22020445</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Clinicopathological features associated with spread through air spaces (STAS) in non-small cell lung cancer: dataset</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr"/>
+      <c r="C566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr"/>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22038864</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2D Mammograms Multiview + DeepSight Cancer Annotations</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr"/>
+      <c r="C567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr"/>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/HYFOWN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G567"/>
+  <dimension ref="A1:G571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12339,6 +12339,90 @@
         </is>
       </c>
     </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Thyroid Cancer Ultrasound Dataset</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr"/>
+      <c r="C568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr"/>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/rahatulislamshahi/thyroid-cancer-ultrasound-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Supplementary Review Package S2 v2.2.11 for Failure-Oriented Evaluation of Deep Learning for Glioma MRI Segmentation: A Release-Aware Method Survey</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr"/>
+      <c r="C569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr"/>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22045219</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>OpenSwissHCC: a multiparametric liver MRI dataset with multiple tumor and liver segmentations of pre-treatment hepatocellular carcinomas</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr"/>
+      <c r="C570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr"/>
+      <c r="F570" t="inlineStr"/>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21992461</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Dataset for article Hybrid thermoresponsive κ-carrageenan-based polymer nanogels respond differently to mono- and divalent metal cations</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr"/>
+      <c r="C571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr"/>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22013218</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G571"/>
+  <dimension ref="A1:G576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12423,6 +12423,111 @@
         </is>
       </c>
     </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Brain Stroke CT Dataset (only PNGs)</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr"/>
+      <c r="C572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr"/>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/narzullayevmirjalol/brain-stroke-ct-dataset-only-pngs</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Eye Disease Image Dataset</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr"/>
+      <c r="C573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr"/>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ahsiulkarim/eye-disease-image-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Bounding the Effect of a Regularized Gate and Handcrafted Features in Patient-Grouped Chest Radiograph Classification</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr"/>
+      <c r="C574" t="inlineStr"/>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr"/>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21988130</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>BreasTomo-Synth: An in silico-generated Digital Breast Tomosynthesis dataset for AI-based tumor segmentation</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr"/>
+      <c r="C575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr"/>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21450435</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Converted TensorFlow Lite models for Accuracy, latency and cross-device reproducibility of four quantisation formats in cross-dataset breast-ultrasound segmentation at the edge</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr"/>
+      <c r="C576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr"/>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21985544</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G576"/>
+  <dimension ref="A1:G592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12528,6 +12528,342 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Knee MRI - Fine Spacing Corpus</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr"/>
+      <c r="C577" t="inlineStr"/>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr"/>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/dreaddevelopment/raptor-knee-finespacing</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Knee MRI - Native 384 Dense Corpus</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr"/>
+      <c r="C578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr"/>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/dreaddevelopment/raptor-knee-native384dense</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Knee MRI - Native 384 Corpus</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr"/>
+      <c r="C579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr"/>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/dreaddevelopment/raptor-knee-native384</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Knee MRI - Full-Span Corpus</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr"/>
+      <c r="C580" t="inlineStr"/>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr"/>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/dreaddevelopment/raptor-knee-fullspan</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Knee MRI - Wide FOV Corpus</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr"/>
+      <c r="C581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr"/>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/dreaddevelopment/raptor-knee-widefov</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Knee MRI - Max-Span Dense Corpus</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr"/>
+      <c r="C582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr"/>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/dreaddevelopment/raptor-knee-maxspan</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Multi-Modal Retinal images for in-depth DR (MMRDR)</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr"/>
+      <c r="C583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Retinal Image</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr"/>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/haashaatif/multi-modal-retinal-images-for-in-depth-dr-mmrdr</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>DRIVE - Retinal Vessel Segmentation</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr"/>
+      <c r="C584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Retinal Image</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr"/>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/namnguynnnn/drive-vessel</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>CHASE DB1 - Retinal Vessel Segmentation</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr"/>
+      <c r="C585" t="inlineStr"/>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Retinal Image</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr"/>
+      <c r="F585" t="inlineStr"/>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/namnguynnnn/chase-db1</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>tetracta/llm-xray-lesion-scans</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr"/>
+      <c r="C586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr"/>
+      <c r="F586" t="inlineStr"/>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/tetracta/llm-xray-lesion-scans</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>jwtyar/WSI-Artifact-Dataset</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr"/>
+      <c r="C587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr"/>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/jwtyar/WSI-Artifact-Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Mindboggle-101: 101 human brain MRI volumes and surfaces, derived templates, and anatomically labeled atlases</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr"/>
+      <c r="C588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr"/>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22070005</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Autonomous multimodal language-model agents for oral lesion diagnosis: dependence on written clinicopathologic context — dataset</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr"/>
+      <c r="C589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr"/>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21582317</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>RuO2 XPS Full-Scan Data and MORPH-XRAY ROI Analysis Outputs</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr"/>
+      <c r="C590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr"/>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22069202</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>MSN-TCSeg: A Transcranial Sonography Dataset for Midbrain and Substantia Nigra Hyperechogenicity Segmentation</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr"/>
+      <c r="C591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr"/>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22065614</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Reproducibility package for cross-dataset transcriptomic analysis of stage-associated hepatic-to-myeloid remodeling in colorectal cancer liver metastasis</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr"/>
+      <c r="C592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr"/>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22076574</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G592"/>
+  <dimension ref="A1:G597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12864,6 +12864,111 @@
         </is>
       </c>
     </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Medical Image Dataset - MRI CT Ultrasound</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr"/>
+      <c r="C593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr"/>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ghofranemalek/medical-image-dataset-mri-ct-ultrasound</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Synthetic HAM10000 Extension Dataset</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr"/>
+      <c r="C594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr"/>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/safrinakabir/synthetic-ham10000-extension-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Unsupervised Anomaly Detection in Pediatric Brains: Method Comparison Across Multiple Clinical Conditions</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr"/>
+      <c r="C595" t="inlineStr"/>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr"/>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21701865</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Imaging dataset for: Beyond the Vessel: Muscle Tissue Oxygenation Kinetics as a Biomarker in Peripheral Arterial Disease</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr"/>
+      <c r="C596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr"/>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22044239</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>MiDAS: A Multimodal Data Acquisition System for Robot Assisted Minimally Invasive Surgery</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr"/>
+      <c r="C597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr"/>
+      <c r="F597" t="inlineStr"/>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/KDQAGC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G597"/>
+  <dimension ref="A1:G603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12969,6 +12969,132 @@
         </is>
       </c>
     </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Dataset for Building Tuberculosis Detectors</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr"/>
+      <c r="C598" t="inlineStr"/>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr"/>
+      <c r="F598" t="inlineStr"/>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/nuidelirina/dataset-for-building-tuberculosis-detectors</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Data and code associated with: napari-lattice: A user-friendly image processing tool for lattice light-sheet microscopy data</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr"/>
+      <c r="C599" t="inlineStr"/>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr"/>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22090339</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Data set 3. SEM micrographs of phlogopite-based porous ceramic filters.</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr"/>
+      <c r="C600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Electron Microscopy</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr"/>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22101942</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>SpheroMix: a combined bright-field tumour spheroid segmentation corpus (32,367 images from four datasets)</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr"/>
+      <c r="C601" t="inlineStr"/>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr"/>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22092984</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>SpheroHQ: an expert-curated bright-field tumour spheroid segmentation dataset (22,683 images, 7 cell lines)</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr"/>
+      <c r="C602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr"/>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22092772</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Raw epifluorescence microscopy sequence of labelled actin filaments in an in vitro motility assay</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr"/>
+      <c r="C603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21991618</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G603"/>
+  <dimension ref="A1:G612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13095,6 +13095,195 @@
         </is>
       </c>
     </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>githut-RSNA-MICCAI-Brain-Tumor-Classification-AI</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr"/>
+      <c r="C604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr"/>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/yannicksteph/githut-rsna-miccai-brain-tumor-classification-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Brain Tumor 2D MRI Dataset</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr"/>
+      <c r="C605" t="inlineStr"/>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr"/>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/bholadev58/brain-tumor-2d-mri-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Thyroid UltraSound Classification</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr"/>
+      <c r="C606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr"/>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/imrul1052/thyroid-ultrasound-classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Wood Species Image Dataset (WSID)</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr"/>
+      <c r="C607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr"/>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/stillniloy/wood-species-image-dataset-wsid</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>FSL Utilities Practice Dataset 2</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr"/>
+      <c r="C608" t="inlineStr"/>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr"/>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22119582</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Photobiomodulation fMRI Dataset</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr"/>
+      <c r="C609" t="inlineStr"/>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr"/>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22114609</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Photobiomodulation fMRI Dataset</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr"/>
+      <c r="C610" t="inlineStr"/>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>fMRI</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr"/>
+      <c r="F610" t="inlineStr"/>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22112141</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Multi-Anatomical Ultrafast Ultrasound Dataset: Raw RF Signals acquired with a GE 11L-D probe</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr"/>
+      <c r="C611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr"/>
+      <c r="F611" t="inlineStr"/>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22125184</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Supplementary material for the article:  Rotating a petavoxel reconstruction exposes the viewing-angle bias inherent to Golgi-Cox and confocal dendritic-spine classification</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr"/>
+      <c r="C612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Confocal Microscopy</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr"/>
+      <c r="F612" t="inlineStr"/>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22118500</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G612"/>
+  <dimension ref="A1:G621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13284,6 +13284,195 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Brain Age MRI Dataset</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr"/>
+      <c r="C613" t="inlineStr"/>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr"/>
+      <c r="F613" t="inlineStr"/>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/radinjunayed22/brain-age-mri-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Rijeka Knee MRI Dataset</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr"/>
+      <c r="C614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr"/>
+      <c r="F614" t="inlineStr"/>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/techtech69/rijeka-knee-mri-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>ADNI MRI Image</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr"/>
+      <c r="C615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr"/>
+      <c r="F615" t="inlineStr"/>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/rashidasif/adni-mri-image</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Robot-assisted Automated Serial-sectioning and Imaging (RASI) Dataset of a Low-temperature Cofired Ceramic Sample</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr"/>
+      <c r="C616" t="inlineStr"/>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr"/>
+      <c r="F616" t="inlineStr"/>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21983581</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Reproduction package: AI-based framework for automated contaminant recognition — detection and quantification of asbestos in recycled gypsum with wide-angle X-ray scattering</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr"/>
+      <c r="C617" t="inlineStr"/>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr"/>
+      <c r="F617" t="inlineStr"/>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22141979</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Lacey carbon grid image dataset</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr"/>
+      <c r="C618" t="inlineStr"/>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr"/>
+      <c r="F618" t="inlineStr"/>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22114065</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Dataset: Work Function and High-Coverage Adsorption Energy as Hydrogen-Evolution Descriptors on Ag-Au-Pd-Pt Alloys</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr"/>
+      <c r="C619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr"/>
+      <c r="F619" t="inlineStr"/>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22031607</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>SPC-Clean: Sample data accompanying the manuscript "SPC-Clean: A napari Plugin for Reducing Speckle and Isolated Pixel Noise in Fluorescence Microscopy Images"</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr"/>
+      <c r="C620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr"/>
+      <c r="F620" t="inlineStr"/>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21934521</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Updated Dataset for paper From Deposition Stress to Surface Reactivity: Strain-Dependent Hydrogen Evolution on Sputtered Platinum Thin Films</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr"/>
+      <c r="C621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr"/>
+      <c r="F621" t="inlineStr"/>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22140361</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G621"/>
+  <dimension ref="A1:G626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13473,6 +13473,111 @@
         </is>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>X-Ray Contraband Detection Dataset</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr"/>
+      <c r="C622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr"/>
+      <c r="F622" t="inlineStr"/>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/banan41k/xray-contraband-detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Multimodal GI Disease Image Dataset</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr"/>
+      <c r="C623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr"/>
+      <c r="F623" t="inlineStr"/>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/rahult25/multimodal-gi-disease-image-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Dataset for paper on Sub-femtosecond XFEL pulse generation at SACLA</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr"/>
+      <c r="C624" t="inlineStr"/>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr"/>
+      <c r="F624" t="inlineStr"/>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22090997</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Code and data accompanying the article "Measuring Data Leakage in the Absence of Patient Identifiers: A Public Kidney CT Benchmark and a Transferable Screen"</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr"/>
+      <c r="C625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr"/>
+      <c r="F625" t="inlineStr"/>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22150980</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>A dataset of cardio-mechanical signals from patients with coronary artery disease undergoing bypass surgery</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr"/>
+      <c r="C626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr"/>
+      <c r="F626" t="inlineStr"/>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22144463</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G626"/>
+  <dimension ref="A1:G631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13578,6 +13578,111 @@
         </is>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>X-Ray Contraband Detection (YOLO format)</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr"/>
+      <c r="C627" t="inlineStr"/>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>X-ray</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr"/>
+      <c r="F627" t="inlineStr"/>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/banan41k/xray-contraband-yolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Advance Caries dataset</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr"/>
+      <c r="C628" t="inlineStr"/>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr"/>
+      <c r="F628" t="inlineStr"/>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/babhero/advance-caries-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Wound-Healing Collagen Fiber Imaging Dataset</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr"/>
+      <c r="C629" t="inlineStr"/>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr"/>
+      <c r="F629" t="inlineStr"/>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22161880</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>OnSight Pathology: A real-time platform-agnostic computational pathology companion for histopathology melanoma and muscle biopsy dataset</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr"/>
+      <c r="C630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Histopathology</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr"/>
+      <c r="F630" t="inlineStr"/>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22167167</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>dataset for Behavioural and neuroendocrine correlates of swimming exercise choice in juvenile Atlantic salmon</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr"/>
+      <c r="C631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr"/>
+      <c r="F631" t="inlineStr"/>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22162227</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G631"/>
+  <dimension ref="A1:G635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13683,6 +13683,90 @@
         </is>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Brain Tumor MRI Dataset Deduplicated</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr"/>
+      <c r="C632" t="inlineStr"/>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr"/>
+      <c r="F632" t="inlineStr"/>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/adamrobertsfiap/brain-tumor-mri-dataset-deduplicated</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Breast Ultrasound normal abnormal Dataset</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr"/>
+      <c r="C633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr"/>
+      <c r="F633" t="inlineStr"/>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/jameswoodmed/breast-ultrasound-normal-abnormal-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>WAW-TACE-2: A Multiparametric MRI Dataset of Hepatocellular Carcinoma Treated with Transarterial Chemoembolization with Tumor and Multi-Organ Segmentations and Clinical Outcomes</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr"/>
+      <c r="C634" t="inlineStr"/>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr"/>
+      <c r="F634" t="inlineStr"/>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/20544500</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>TumorQuantAI colon cancer CD3, CD8, and CK20 whole-slide image dataset</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr"/>
+      <c r="C635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr"/>
+      <c r="F635" t="inlineStr"/>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22177196</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G635"/>
+  <dimension ref="A1:G646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13767,6 +13767,237 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Unified Dental Panoramic FDI YOLO Dataset</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr"/>
+      <c r="C636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr"/>
+      <c r="F636" t="inlineStr"/>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/kosett/unified-dental-panoramic-fdi-yolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>GA-Epoxy Wear Scar Microscopy Dataset</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr"/>
+      <c r="C637" t="inlineStr"/>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr"/>
+      <c r="F637" t="inlineStr"/>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/maulikgajera/ga-epoxy-wear-scar-microscopy-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>HAM10000 — Standardized Preprocessed Dataset</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr"/>
+      <c r="C638" t="inlineStr"/>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr"/>
+      <c r="F638" t="inlineStr"/>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/hosseinsimchidev/ham10000-preprocessed-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Reference segmentations of tumour and resection cavity for the ReMIND cohort (ioUS-to-MR synthesis benchmark)</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr"/>
+      <c r="C639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr"/>
+      <c r="F639" t="inlineStr"/>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22214975</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>BrainSaw gad tdTomato example dataset</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr"/>
+      <c r="C640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr"/>
+      <c r="F640" t="inlineStr"/>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22114628</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Dataset for: Quantifying post-depositional surface modification on Middle and Late Pleistocene quartz artefacts from the EDAR sites, Eastern Desert, Sudan</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr"/>
+      <c r="C641" t="inlineStr"/>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr"/>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/21194442</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>BoneMarrowWSI-PediatricLeukemia: A Comprehensive Dataset of Bone Marrow Aspirate Smear Whole Slide Images with Expert Annotations and Clinical Data in Pediatric Leukemia</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr"/>
+      <c r="C642" t="inlineStr"/>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Whole Slide Imaging</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr"/>
+      <c r="F642" t="inlineStr"/>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/18499180</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Evaluation of AI-based segmentation and synthetic CT generation for MRI-only prostate radiotherapy planning.</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr"/>
+      <c r="C643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr"/>
+      <c r="F643" t="inlineStr"/>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13504376/</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Efficient and rapid generation of high-quality CT images from CBCT using a flow matching model.</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr"/>
+      <c r="C644" t="inlineStr"/>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>CBCT</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr"/>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13486935/</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Released_LLFS</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr"/>
+      <c r="C645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr"/>
+      <c r="F645" t="inlineStr"/>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>https://www.synapse.org/Synapse:syn52663596</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Documentary Wedding Photography in Romania: Moment Taxonomy and Planning Dataset</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr"/>
+      <c r="C646" t="inlineStr"/>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr"/>
+      <c r="F646" t="inlineStr"/>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/85YBGQ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G646"/>
+  <dimension ref="A1:G653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13998,6 +13998,153 @@
         </is>
       </c>
     </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>MRI dataset</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr"/>
+      <c r="C647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr"/>
+      <c r="F647" t="inlineStr"/>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/dari4510/mri-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>UCSF-PDGM-Grade-23-Full-Dataset</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr"/>
+      <c r="C648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr"/>
+      <c r="F648" t="inlineStr"/>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/vihansanthosh/ucsf-pdgm-grade23-full</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Breast Cancer Mammography Image Datasets</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr"/>
+      <c r="C649" t="inlineStr"/>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr"/>
+      <c r="F649" t="inlineStr"/>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/esubalewasmare/breast-cancer-mammography-image-datasets</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Breast Cancer Ultrasound Image Datasets</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr"/>
+      <c r="C650" t="inlineStr"/>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr"/>
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/esubalewasmare/breast-cancer-ultrasound-image-datasets</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Cholecystitis Multimodal Image Dataset</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr"/>
+      <c r="C651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr"/>
+      <c r="F651" t="inlineStr"/>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/rahult25/cholecystitis-multimodal-image-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>AgriDoc-PK Crop Disease Dataset</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr"/>
+      <c r="C652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr"/>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/mubashiruddin01/agridoc-pk-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>CT texture phantom dataset with paired image quality assessments for quantitative imaging.</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr"/>
+      <c r="C653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr"/>
+      <c r="F653" t="inlineStr"/>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC13527279/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G653"/>
+  <dimension ref="A1:G663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14145,6 +14145,217 @@
         </is>
       </c>
     </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Covid-19 CT Scan</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr"/>
+      <c r="C654" t="inlineStr"/>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr"/>
+      <c r="F654" t="inlineStr"/>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/pawankr12/covid-19-ct-scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Diabetic Macular Edema OCT Image Dataset</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr"/>
+      <c r="C655" t="inlineStr"/>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr"/>
+      <c r="F655" t="inlineStr"/>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/ucimachinelearning/diabetic-macular-edema-oct-image-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Macular Dataset OCT</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr"/>
+      <c r="C656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr"/>
+      <c r="F656" t="inlineStr"/>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/deepakraje24phd0186/macular-dataset-oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Dataset of "Real-time probing of adsorption dynamics on Pt nanoparticles: Competitive
+interactions and site blocking in electrocatalysis"</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr"/>
+      <c r="C657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr"/>
+      <c r="F657" t="inlineStr"/>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22273113</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Dataset of "From Surface to Bulk and Back: Dynamic Redistribution of Iron in CeO2(111) Model Catalysts under Reducing and Oxidizing Conditions"</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr"/>
+      <c r="C658" t="inlineStr"/>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr"/>
+      <c r="F658" t="inlineStr"/>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22253116</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Genetic Insights into Head-to-Body Ratios Via Deep Learning-Based Image Segmentation and Implications for Common Diseases</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr"/>
+      <c r="C659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr"/>
+      <c r="F659" t="inlineStr"/>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22264855</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>upporting data and code for "Geometric, acquisition and image-formation limits of two-dimensional ultrasound volumetry across simulated fluid-filled structures"</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr"/>
+      <c r="C660" t="inlineStr"/>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr"/>
+      <c r="F660" t="inlineStr"/>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22258803</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Early treatment of cutaneous neurofibromas type 1 (cNF) to markedly improve patient's quality of life</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr"/>
+      <c r="C661" t="inlineStr"/>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="inlineStr"/>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>https://www.synapse.org/Synapse:syn31619419</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>A deep learning microscopy framework for NF1 patient-derived organoid drug screening</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr"/>
+      <c r="C662" t="inlineStr"/>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr"/>
+      <c r="F662" t="inlineStr"/>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>https://www.synapse.org/Synapse:syn62031004</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Use of the mouse model of cutaneous neurofibromas for identification of cells of origin and drug screening studies</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr"/>
+      <c r="C663" t="inlineStr"/>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="inlineStr"/>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>https://www.synapse.org/Synapse:syn11374337</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G663"/>
+  <dimension ref="A1:G666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14356,6 +14356,69 @@
         </is>
       </c>
     </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Dental Dataset</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr"/>
+      <c r="C664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr"/>
+      <c r="F664" t="inlineStr"/>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/obaidulhaque/dental-dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Dataset for the paper ''Characterizing the Spatiotemporal Boundaries of Functional Ultrasound for Brain Decoding"</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr"/>
+      <c r="C665" t="inlineStr"/>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Ultrasound</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr"/>
+      <c r="F665" t="inlineStr"/>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22283977</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>BrainSaw sst tdTomato example dataset</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr"/>
+      <c r="C666" t="inlineStr"/>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr"/>
+      <c r="F666" t="inlineStr"/>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22232268</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/new_datasets.xlsx
+++ b/new_datasets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G666"/>
+  <dimension ref="A1:G673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14419,6 +14419,153 @@
         </is>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Brain MRI Images</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr"/>
+      <c r="C667" t="inlineStr"/>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr"/>
+      <c r="F667" t="inlineStr"/>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/solaman/brain-mri-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Mendeley Brain Tumor MRI Dataset V6</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr"/>
+      <c r="C668" t="inlineStr"/>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>MRI</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="inlineStr"/>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/datasets/solaman/mendeley-brain-tumor-mri-dataset-v6</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Sulfotransferases (SULTs) interaction whit amyloid PET tracers dataset</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr"/>
+      <c r="C669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>PET</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr"/>
+      <c r="F669" t="inlineStr"/>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22304099</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Data for "Internal adaptation of CAD/CAM post-and-core restorations using prefabricated versus digitally derived scan posts: an in vitro micro-CT analysis"</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr"/>
+      <c r="C670" t="inlineStr"/>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Micro-CT</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr"/>
+      <c r="F670" t="inlineStr"/>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22302388</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Galicia marine finfish aquaculture production dataset</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr"/>
+      <c r="C671" t="inlineStr"/>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr"/>
+      <c r="F671" t="inlineStr"/>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22307874</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Turbot production dataset: capture fisheries and aquaculture (1950–2023)</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr"/>
+      <c r="C672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Medical Imaging</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr"/>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/22307761</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Data associated with American Heart Association grant, 23AIREA1053137, Functional consequences of cardiomyopathy mutations in alpha-actinin</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr"/>
+      <c r="C673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Microscopy</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr"/>
+      <c r="F673" t="inlineStr"/>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/IDO9IC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
